--- a/LIST ANGGOTA KKCS PERIODE 2026 FIX.xlsx
+++ b/LIST ANGGOTA KKCS PERIODE 2026 FIX.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01. KERJA\K K C S\Laporan Bulanan\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kerja\kkcs-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8CDFC6-8D7F-4BF7-B8B5-E9527043FB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CDE3FB7-7286-4BCC-866B-5D4CA2246F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{97CE4977-F499-468B-9AC7-D6C68C1EF891}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{97CE4977-F499-468B-9AC7-D6C68C1EF891}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -747,7 +758,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -840,7 +851,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -868,6 +879,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1469,9 +1486,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1480,10 +1497,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1494,16 +1511,16 @@
     <xf numFmtId="17" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1511,41 +1528,41 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="9" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1554,25 +1571,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1605,22 +1622,22 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="17" fontId="9" fillId="4" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1630,6 +1647,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="9" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1662,19 +1692,8 @@
     <xf numFmtId="17" fontId="9" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1699,9 +1718,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1739,7 +1758,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1845,7 +1864,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1987,7 +2006,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1999,68 +2018,68 @@
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="A1:BJ108"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="4.5703125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="9.140625" style="2"/>
-    <col min="5" max="5" width="29.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="4.42578125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="4.42578125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="13.28515625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="6.5703125" style="56" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="13.28515625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="6.5703125" style="56" customWidth="1"/>
-    <col min="18" max="18" width="13.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13.28515625" style="2" customWidth="1"/>
-    <col min="21" max="21" width="6.5703125" style="56" customWidth="1"/>
-    <col min="22" max="22" width="13.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.28515625" style="2" customWidth="1"/>
-    <col min="25" max="25" width="6.5703125" style="56" customWidth="1"/>
-    <col min="26" max="26" width="13.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.5703125" style="56" customWidth="1"/>
-    <col min="30" max="30" width="13.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.5703125" style="56" customWidth="1"/>
-    <col min="34" max="34" width="13.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="2"/>
-    <col min="36" max="36" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="6.5703125" style="56" customWidth="1"/>
-    <col min="38" max="38" width="13.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="6.5703125" style="56" customWidth="1"/>
-    <col min="42" max="42" width="13.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="9.140625" style="2"/>
-    <col min="44" max="44" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="6.5703125" style="56" customWidth="1"/>
-    <col min="46" max="46" width="13.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="6.5703125" style="56" customWidth="1"/>
-    <col min="50" max="50" width="13.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="6.5703125" style="56" customWidth="1"/>
-    <col min="54" max="54" width="13.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="6.5703125" style="56" customWidth="1"/>
-    <col min="58" max="58" width="13.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="6.5703125" style="56" customWidth="1"/>
-    <col min="62" max="62" width="11.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="63" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="2" width="4.54296875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="9.1796875" style="2"/>
+    <col min="5" max="5" width="29.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="4.453125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="13.26953125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="4.453125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="13.26953125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="6.54296875" style="56" customWidth="1"/>
+    <col min="14" max="14" width="13.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="13.26953125" style="2" customWidth="1"/>
+    <col min="17" max="17" width="6.54296875" style="56" customWidth="1"/>
+    <col min="18" max="18" width="13.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="13.26953125" style="2" customWidth="1"/>
+    <col min="21" max="21" width="6.54296875" style="56" customWidth="1"/>
+    <col min="22" max="22" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="13.26953125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="6.54296875" style="56" customWidth="1"/>
+    <col min="26" max="26" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.54296875" style="56" customWidth="1"/>
+    <col min="30" max="30" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.54296875" style="56" customWidth="1"/>
+    <col min="34" max="34" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="2"/>
+    <col min="36" max="36" width="12.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6.54296875" style="56" customWidth="1"/>
+    <col min="38" max="38" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="6.54296875" style="56" customWidth="1"/>
+    <col min="42" max="42" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="9.1796875" style="2"/>
+    <col min="44" max="44" width="12.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="6.54296875" style="56" customWidth="1"/>
+    <col min="46" max="46" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="12.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="6.54296875" style="56" customWidth="1"/>
+    <col min="50" max="50" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="6.54296875" style="56" customWidth="1"/>
+    <col min="54" max="54" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="12.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="12.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="6.54296875" style="56" customWidth="1"/>
+    <col min="58" max="58" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="6.54296875" style="56" customWidth="1"/>
+    <col min="62" max="62" width="11.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="63" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" ht="13.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:61" ht="13" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J1" s="4">
         <f>SUM(J5:J104)</f>
         <v>9000000</v>
@@ -2227,66 +2246,66 @@
       </c>
       <c r="BI1" s="80"/>
     </row>
-    <row r="2" spans="1:61" ht="12.75" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:61" ht="12.5" thickTop="1" x14ac:dyDescent="0.3">
       <c r="N2" s="7"/>
       <c r="P2" s="7"/>
     </row>
-    <row r="3" spans="1:61" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:61" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J3" s="3"/>
-      <c r="L3" s="90" t="s">
-        <v>0</v>
-      </c>
-      <c r="M3" s="90"/>
-      <c r="N3" s="90"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="90"/>
-      <c r="Q3" s="90"/>
-      <c r="R3" s="90"/>
-      <c r="S3" s="90"/>
-      <c r="T3" s="90"/>
-      <c r="U3" s="90"/>
-      <c r="V3" s="90"/>
-      <c r="W3" s="90"/>
-      <c r="X3" s="90"/>
-      <c r="Y3" s="90"/>
-      <c r="Z3" s="90"/>
-      <c r="AA3" s="90"/>
-      <c r="AB3" s="90"/>
-      <c r="AC3" s="90"/>
-      <c r="AD3" s="90"/>
-      <c r="AE3" s="90"/>
-      <c r="AF3" s="90"/>
-      <c r="AG3" s="90"/>
-      <c r="AH3" s="90"/>
-      <c r="AI3" s="90"/>
-      <c r="AJ3" s="90"/>
-      <c r="AK3" s="90"/>
-      <c r="AL3" s="90"/>
-      <c r="AM3" s="90"/>
-      <c r="AN3" s="90"/>
-      <c r="AO3" s="90"/>
-      <c r="AP3" s="90"/>
-      <c r="AQ3" s="90"/>
-      <c r="AR3" s="90"/>
-      <c r="AS3" s="90"/>
-      <c r="AT3" s="90"/>
-      <c r="AU3" s="90"/>
-      <c r="AV3" s="90"/>
-      <c r="AW3" s="90"/>
-      <c r="AX3" s="90"/>
-      <c r="AY3" s="90"/>
-      <c r="AZ3" s="90"/>
-      <c r="BA3" s="90"/>
-      <c r="BB3" s="90"/>
-      <c r="BC3" s="90"/>
-      <c r="BD3" s="90"/>
-      <c r="BE3" s="90"/>
-      <c r="BF3" s="90"/>
-      <c r="BG3" s="90"/>
-      <c r="BH3" s="90"/>
+      <c r="L3" s="95" t="s">
+        <v>0</v>
+      </c>
+      <c r="M3" s="95"/>
+      <c r="N3" s="95"/>
+      <c r="O3" s="95"/>
+      <c r="P3" s="95"/>
+      <c r="Q3" s="95"/>
+      <c r="R3" s="95"/>
+      <c r="S3" s="95"/>
+      <c r="T3" s="95"/>
+      <c r="U3" s="95"/>
+      <c r="V3" s="95"/>
+      <c r="W3" s="95"/>
+      <c r="X3" s="95"/>
+      <c r="Y3" s="95"/>
+      <c r="Z3" s="95"/>
+      <c r="AA3" s="95"/>
+      <c r="AB3" s="95"/>
+      <c r="AC3" s="95"/>
+      <c r="AD3" s="95"/>
+      <c r="AE3" s="95"/>
+      <c r="AF3" s="95"/>
+      <c r="AG3" s="95"/>
+      <c r="AH3" s="95"/>
+      <c r="AI3" s="95"/>
+      <c r="AJ3" s="95"/>
+      <c r="AK3" s="95"/>
+      <c r="AL3" s="95"/>
+      <c r="AM3" s="95"/>
+      <c r="AN3" s="95"/>
+      <c r="AO3" s="95"/>
+      <c r="AP3" s="95"/>
+      <c r="AQ3" s="95"/>
+      <c r="AR3" s="95"/>
+      <c r="AS3" s="95"/>
+      <c r="AT3" s="95"/>
+      <c r="AU3" s="95"/>
+      <c r="AV3" s="95"/>
+      <c r="AW3" s="95"/>
+      <c r="AX3" s="95"/>
+      <c r="AY3" s="95"/>
+      <c r="AZ3" s="95"/>
+      <c r="BA3" s="95"/>
+      <c r="BB3" s="95"/>
+      <c r="BC3" s="95"/>
+      <c r="BD3" s="95"/>
+      <c r="BE3" s="95"/>
+      <c r="BF3" s="95"/>
+      <c r="BG3" s="95"/>
+      <c r="BH3" s="95"/>
       <c r="BI3" s="2"/>
     </row>
-    <row r="4" spans="1:61" s="10" customFormat="1" ht="13.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:61" s="10" customFormat="1" ht="13" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9">
         <v>2025</v>
       </c>
@@ -2317,104 +2336,104 @@
       <c r="M4" s="54" t="s">
         <v>213</v>
       </c>
-      <c r="N4" s="91">
+      <c r="N4" s="96">
         <v>45658</v>
       </c>
-      <c r="O4" s="92"/>
-      <c r="P4" s="93"/>
+      <c r="O4" s="97"/>
+      <c r="P4" s="98"/>
       <c r="Q4" s="81" t="s">
         <v>213</v>
       </c>
-      <c r="R4" s="84">
+      <c r="R4" s="89">
         <v>45689</v>
       </c>
-      <c r="S4" s="85"/>
-      <c r="T4" s="86"/>
+      <c r="S4" s="90"/>
+      <c r="T4" s="91"/>
       <c r="U4" s="82" t="s">
         <v>213</v>
       </c>
-      <c r="V4" s="87">
+      <c r="V4" s="92">
         <v>45717</v>
       </c>
-      <c r="W4" s="88"/>
-      <c r="X4" s="89"/>
+      <c r="W4" s="93"/>
+      <c r="X4" s="94"/>
       <c r="Y4" s="81" t="s">
         <v>213</v>
       </c>
-      <c r="Z4" s="84">
+      <c r="Z4" s="89">
         <v>45748</v>
       </c>
-      <c r="AA4" s="85"/>
-      <c r="AB4" s="86"/>
+      <c r="AA4" s="90"/>
+      <c r="AB4" s="91"/>
       <c r="AC4" s="82" t="s">
         <v>213</v>
       </c>
-      <c r="AD4" s="87">
+      <c r="AD4" s="92">
         <v>45778</v>
       </c>
-      <c r="AE4" s="88"/>
-      <c r="AF4" s="89"/>
+      <c r="AE4" s="93"/>
+      <c r="AF4" s="94"/>
       <c r="AG4" s="81" t="s">
         <v>213</v>
       </c>
-      <c r="AH4" s="84">
+      <c r="AH4" s="89">
         <v>45809</v>
       </c>
-      <c r="AI4" s="85"/>
-      <c r="AJ4" s="86"/>
+      <c r="AI4" s="90"/>
+      <c r="AJ4" s="91"/>
       <c r="AK4" s="82" t="s">
         <v>213</v>
       </c>
-      <c r="AL4" s="87">
+      <c r="AL4" s="92">
         <v>45839</v>
       </c>
-      <c r="AM4" s="88"/>
-      <c r="AN4" s="89"/>
+      <c r="AM4" s="93"/>
+      <c r="AN4" s="94"/>
       <c r="AO4" s="81" t="s">
         <v>213</v>
       </c>
-      <c r="AP4" s="84">
+      <c r="AP4" s="89">
         <v>45870</v>
       </c>
-      <c r="AQ4" s="85"/>
-      <c r="AR4" s="86"/>
+      <c r="AQ4" s="90"/>
+      <c r="AR4" s="91"/>
       <c r="AS4" s="82" t="s">
         <v>213</v>
       </c>
-      <c r="AT4" s="87">
+      <c r="AT4" s="92">
         <v>45901</v>
       </c>
-      <c r="AU4" s="88"/>
-      <c r="AV4" s="89"/>
+      <c r="AU4" s="93"/>
+      <c r="AV4" s="94"/>
       <c r="AW4" s="81" t="s">
         <v>213</v>
       </c>
-      <c r="AX4" s="84">
+      <c r="AX4" s="89">
         <v>45931</v>
       </c>
-      <c r="AY4" s="85"/>
-      <c r="AZ4" s="86"/>
+      <c r="AY4" s="90"/>
+      <c r="AZ4" s="91"/>
       <c r="BA4" s="82" t="s">
         <v>213</v>
       </c>
-      <c r="BB4" s="87">
+      <c r="BB4" s="92">
         <v>45962</v>
       </c>
-      <c r="BC4" s="88"/>
-      <c r="BD4" s="89"/>
+      <c r="BC4" s="93"/>
+      <c r="BD4" s="94"/>
       <c r="BE4" s="81" t="s">
         <v>213</v>
       </c>
-      <c r="BF4" s="84">
+      <c r="BF4" s="89">
         <v>45992</v>
       </c>
-      <c r="BG4" s="85"/>
-      <c r="BH4" s="86"/>
+      <c r="BG4" s="90"/>
+      <c r="BH4" s="91"/>
       <c r="BI4" s="83" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="5" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -2617,7 +2636,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -2820,7 +2839,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="7" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -3023,7 +3042,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="8" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -3226,7 +3245,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -3429,7 +3448,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -3632,7 +3651,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="11" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -3835,7 +3854,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="12" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -4038,7 +4057,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -4241,7 +4260,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="14" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -4444,7 +4463,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="15" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -4647,7 +4666,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="16" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -4850,7 +4869,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="17" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -5053,7 +5072,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="18" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -5256,7 +5275,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="19" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -5459,7 +5478,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="20" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -5662,7 +5681,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="21" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -5865,7 +5884,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="22" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -6068,7 +6087,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="23" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -6271,7 +6290,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="24" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -6474,7 +6493,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="25" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -6677,7 +6696,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="26" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -6880,7 +6899,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="27" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -7083,7 +7102,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="28" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -7286,7 +7305,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="29" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -7489,7 +7508,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="30" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -7692,7 +7711,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="31" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -7896,7 +7915,7 @@
       </c>
       <c r="BJ31" s="7"/>
     </row>
-    <row r="32" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -8099,7 +8118,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="33" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -8302,7 +8321,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="34" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -8505,7 +8524,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="35" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -8708,7 +8727,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -8911,7 +8930,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="37" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -9114,7 +9133,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="38" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -9317,7 +9336,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -9520,7 +9539,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="40" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -9723,7 +9742,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="41" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -9926,7 +9945,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="42" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -10129,7 +10148,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="43" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -10332,7 +10351,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="44" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -10535,7 +10554,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="45" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -10738,7 +10757,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="46" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -10941,7 +10960,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="47" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -11144,7 +11163,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="48" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -11347,7 +11366,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="49" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -11550,7 +11569,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="50" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -11753,7 +11772,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -11956,7 +11975,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="52" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -12159,7 +12178,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="53" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -12362,7 +12381,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="54" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -12565,7 +12584,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="55" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -12768,7 +12787,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="56" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -12971,7 +12990,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -13174,7 +13193,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="58" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -13377,7 +13396,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="59" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -13580,7 +13599,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="60" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -13783,7 +13802,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="61" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -13986,7 +14005,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="62" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>62</v>
       </c>
@@ -14189,7 +14208,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="63" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>63</v>
       </c>
@@ -14392,7 +14411,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="64" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>64</v>
       </c>
@@ -14595,7 +14614,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="65" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>65</v>
       </c>
@@ -14798,7 +14817,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="66" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>66</v>
       </c>
@@ -15001,7 +15020,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="67" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>67</v>
       </c>
@@ -15204,7 +15223,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="68" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>68</v>
       </c>
@@ -15407,7 +15426,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="69" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>69</v>
       </c>
@@ -15610,7 +15629,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="70" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>70</v>
       </c>
@@ -15813,7 +15832,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="71" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>71</v>
       </c>
@@ -16016,7 +16035,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="72" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>72</v>
       </c>
@@ -16219,7 +16238,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="73" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>73</v>
       </c>
@@ -16422,7 +16441,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="74" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>74</v>
       </c>
@@ -16625,7 +16644,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="75" spans="1:61" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:61" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>75</v>
       </c>
@@ -16830,7 +16849,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="76" spans="1:61" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:61" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>76</v>
       </c>
@@ -17035,7 +17054,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="77" spans="1:61" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:61" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="1">
         <v>73</v>
@@ -17232,7 +17251,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:61" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:61" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="1">
         <v>74</v>
@@ -17429,7 +17448,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:61" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:61" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="1">
         <v>75</v>
@@ -17626,7 +17645,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:61" x14ac:dyDescent="0.3">
       <c r="B80" s="1">
         <v>76</v>
       </c>
@@ -17654,8 +17673,8 @@
       <c r="L80" s="25">
         <v>0</v>
       </c>
-      <c r="M80" s="94"/>
-      <c r="N80" s="95">
+      <c r="M80" s="84"/>
+      <c r="N80" s="85">
         <v>0</v>
       </c>
       <c r="O80" s="27">
@@ -17665,8 +17684,8 @@
         <f>L80+N80+O80</f>
         <v>0</v>
       </c>
-      <c r="Q80" s="94"/>
-      <c r="R80" s="95">
+      <c r="Q80" s="84"/>
+      <c r="R80" s="85">
         <v>0</v>
       </c>
       <c r="S80" s="27">
@@ -17676,8 +17695,8 @@
         <f>P80+R80+S80</f>
         <v>0</v>
       </c>
-      <c r="U80" s="94"/>
-      <c r="V80" s="95">
+      <c r="U80" s="84"/>
+      <c r="V80" s="85">
         <v>0</v>
       </c>
       <c r="W80" s="27">
@@ -17687,8 +17706,8 @@
         <f>T80+V80+W80</f>
         <v>0</v>
       </c>
-      <c r="Y80" s="94"/>
-      <c r="Z80" s="95">
+      <c r="Y80" s="84"/>
+      <c r="Z80" s="85">
         <v>0</v>
       </c>
       <c r="AA80" s="27">
@@ -17698,8 +17717,8 @@
         <f>X80+Z80+AA80</f>
         <v>0</v>
       </c>
-      <c r="AC80" s="94"/>
-      <c r="AD80" s="95">
+      <c r="AC80" s="84"/>
+      <c r="AD80" s="85">
         <v>50000</v>
       </c>
       <c r="AE80" s="27">
@@ -17709,7 +17728,7 @@
         <f t="shared" si="28"/>
         <v>50000</v>
       </c>
-      <c r="AG80" s="94">
+      <c r="AG80" s="84">
         <v>1</v>
       </c>
       <c r="AH80" s="26">
@@ -17722,7 +17741,7 @@
         <f t="shared" si="27"/>
         <v>100000</v>
       </c>
-      <c r="AK80" s="94">
+      <c r="AK80" s="84">
         <f t="shared" si="44"/>
         <v>2</v>
       </c>
@@ -17736,7 +17755,7 @@
         <f>AJ80+AL80+AM80</f>
         <v>150000</v>
       </c>
-      <c r="AO80" s="94">
+      <c r="AO80" s="84">
         <f t="shared" si="45"/>
         <v>3</v>
       </c>
@@ -17750,7 +17769,7 @@
         <f>AN80+AP80+AQ80</f>
         <v>200000</v>
       </c>
-      <c r="AS80" s="94">
+      <c r="AS80" s="84">
         <f t="shared" si="46"/>
         <v>4</v>
       </c>
@@ -17764,7 +17783,7 @@
         <f>AR80+AT80+AU80</f>
         <v>250000</v>
       </c>
-      <c r="AW80" s="94">
+      <c r="AW80" s="84">
         <f t="shared" si="47"/>
         <v>5</v>
       </c>
@@ -17778,7 +17797,7 @@
         <f>AV80+AX80+AY80</f>
         <v>250000</v>
       </c>
-      <c r="BA80" s="94">
+      <c r="BA80" s="84">
         <f t="shared" si="48"/>
         <v>5</v>
       </c>
@@ -17792,7 +17811,7 @@
         <f>AZ80+BB80+BC80</f>
         <v>250000</v>
       </c>
-      <c r="BE80" s="94">
+      <c r="BE80" s="84">
         <f t="shared" si="49"/>
         <v>5</v>
       </c>
@@ -17806,12 +17825,12 @@
         <f>BD80+BF80+BG80</f>
         <v>250000</v>
       </c>
-      <c r="BI80" s="96">
+      <c r="BI80" s="86">
         <f t="shared" si="50"/>
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:61" x14ac:dyDescent="0.3">
       <c r="B81" s="1">
         <v>76</v>
       </c>
@@ -17836,7 +17855,7 @@
       <c r="J81" s="18">
         <v>100000</v>
       </c>
-      <c r="K81" s="97"/>
+      <c r="K81" s="87"/>
       <c r="L81" s="18">
         <v>0</v>
       </c>
@@ -17986,7 +18005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:61" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:61" ht="12.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B82" s="1">
         <v>76</v>
       </c>
@@ -18011,7 +18030,7 @@
       <c r="J82" s="30">
         <v>100000</v>
       </c>
-      <c r="K82" s="98"/>
+      <c r="K82" s="88"/>
       <c r="L82" s="30">
         <v>0</v>
       </c>
@@ -18161,7 +18180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:61" s="8" customFormat="1" ht="13.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:61" s="8" customFormat="1" ht="13" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="H83" s="23"/>
@@ -18219,7 +18238,7 @@
       <c r="BH83" s="36"/>
       <c r="BI83" s="57"/>
     </row>
-    <row r="84" spans="1:61" s="38" customFormat="1" ht="12.75" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:61" s="38" customFormat="1" ht="12.5" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="H84" s="39"/>
@@ -18365,7 +18384,7 @@
       </c>
       <c r="BI84" s="75"/>
     </row>
-    <row r="85" spans="1:61" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:61" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>77</v>
       </c>
@@ -18532,7 +18551,7 @@
       </c>
       <c r="BI85" s="71"/>
     </row>
-    <row r="86" spans="1:61" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:61" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>78</v>
       </c>
@@ -18699,7 +18718,7 @@
       </c>
       <c r="BI86" s="71"/>
     </row>
-    <row r="87" spans="1:61" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:61" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>79</v>
       </c>
@@ -18866,7 +18885,7 @@
       </c>
       <c r="BI87" s="71"/>
     </row>
-    <row r="88" spans="1:61" s="38" customFormat="1" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:61" s="38" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="H88" s="39"/>
@@ -19012,8 +19031,8 @@
       </c>
       <c r="BI88" s="76"/>
     </row>
-    <row r="89" spans="1:61" ht="13.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:61" s="38" customFormat="1" ht="12.75" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:61" ht="13" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="90" spans="1:61" s="38" customFormat="1" ht="12.5" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="H90" s="39"/>
@@ -19159,7 +19178,7 @@
       </c>
       <c r="BI90" s="75"/>
     </row>
-    <row r="91" spans="1:61" s="38" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:61" s="38" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="2" t="s">
@@ -19185,7 +19204,7 @@
         <v>100000</v>
       </c>
       <c r="K91" s="39"/>
-      <c r="L91" s="12">
+      <c r="L91" s="99">
         <v>4540000</v>
       </c>
       <c r="M91" s="59"/>
@@ -19322,7 +19341,7 @@
       </c>
       <c r="BI91" s="77"/>
     </row>
-    <row r="92" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:61" x14ac:dyDescent="0.3">
       <c r="C92" s="2" t="s">
         <v>200</v>
       </c>
@@ -19344,7 +19363,7 @@
       <c r="J92" s="18">
         <v>100000</v>
       </c>
-      <c r="L92" s="18">
+      <c r="L92" s="100">
         <v>4940000</v>
       </c>
       <c r="M92" s="60"/>
@@ -19481,7 +19500,7 @@
       </c>
       <c r="BI92" s="78"/>
     </row>
-    <row r="93" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:61" x14ac:dyDescent="0.3">
       <c r="C93" s="2" t="s">
         <v>204</v>
       </c>
@@ -19503,7 +19522,7 @@
       <c r="J93" s="18">
         <v>100000</v>
       </c>
-      <c r="L93" s="18">
+      <c r="L93" s="100">
         <v>3720000</v>
       </c>
       <c r="M93" s="60"/>
@@ -19640,7 +19659,7 @@
       </c>
       <c r="BI93" s="78"/>
     </row>
-    <row r="94" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:61" x14ac:dyDescent="0.3">
       <c r="C94" s="2" t="s">
         <v>207</v>
       </c>
@@ -19662,7 +19681,7 @@
       <c r="J94" s="18">
         <v>100000</v>
       </c>
-      <c r="L94" s="18">
+      <c r="L94" s="100">
         <v>3840000</v>
       </c>
       <c r="M94" s="60"/>
@@ -19799,7 +19818,7 @@
       </c>
       <c r="BI94" s="78"/>
     </row>
-    <row r="95" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:61" x14ac:dyDescent="0.3">
       <c r="C95" s="2" t="s">
         <v>210</v>
       </c>
@@ -19821,7 +19840,7 @@
       <c r="J95" s="18">
         <v>100000</v>
       </c>
-      <c r="L95" s="18">
+      <c r="L95" s="100">
         <v>4140000</v>
       </c>
       <c r="M95" s="60"/>
@@ -19958,7 +19977,7 @@
       </c>
       <c r="BI95" s="78"/>
     </row>
-    <row r="96" spans="1:61" s="38" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:61" s="38" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="2"/>
@@ -20109,7 +20128,7 @@
       </c>
       <c r="BI96" s="79"/>
     </row>
-    <row r="97" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>26</v>
       </c>
@@ -20283,7 +20302,7 @@
       <c r="BI97" s="71"/>
       <c r="BJ97" s="7"/>
     </row>
-    <row r="98" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>41</v>
       </c>
@@ -20457,7 +20476,7 @@
       <c r="BI98" s="71"/>
       <c r="BJ98" s="7"/>
     </row>
-    <row r="99" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>61</v>
       </c>
@@ -20634,7 +20653,7 @@
       <c r="BI99" s="71"/>
       <c r="BJ99" s="7"/>
     </row>
-    <row r="100" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>20</v>
       </c>
@@ -20825,7 +20844,7 @@
       </c>
       <c r="BI100" s="71"/>
     </row>
-    <row r="101" spans="1:62" s="38" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:62" s="38" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="2"/>
@@ -20976,7 +20995,7 @@
       </c>
       <c r="BI101" s="79"/>
     </row>
-    <row r="102" spans="1:62" s="38" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:62" s="38" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="2"/>
@@ -21127,7 +21146,7 @@
       </c>
       <c r="BI102" s="79"/>
     </row>
-    <row r="103" spans="1:62" s="38" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:62" s="38" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="2"/>
@@ -21278,7 +21297,7 @@
       </c>
       <c r="BI103" s="79"/>
     </row>
-    <row r="104" spans="1:62" s="38" customFormat="1" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:62" s="38" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="H104" s="39"/>
@@ -21424,8 +21443,8 @@
       </c>
       <c r="BI104" s="76"/>
     </row>
-    <row r="105" spans="1:62" ht="12.75" thickTop="1" x14ac:dyDescent="0.2"/>
-    <row r="107" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:62" ht="12.5" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="107" spans="1:62" x14ac:dyDescent="0.3">
       <c r="J107" s="7"/>
       <c r="L107" s="7"/>
       <c r="M107" s="63"/>
@@ -21442,7 +21461,7 @@
       <c r="BE107" s="63"/>
       <c r="BI107" s="63"/>
     </row>
-    <row r="108" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:62" x14ac:dyDescent="0.3">
       <c r="J108" s="36"/>
       <c r="L108" s="36"/>
       <c r="M108" s="64"/>
@@ -21511,12 +21530,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F6D9A83-DFE8-424E-89F2-14AA0C7DB351}">
   <dimension ref="A1:N208"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -21539,7 +21558,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -21569,7 +21588,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>175</v>
       </c>
@@ -21599,7 +21618,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -21629,7 +21648,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -21659,7 +21678,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -21689,7 +21708,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -21719,7 +21738,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -21749,7 +21768,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -21779,7 +21798,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -21809,7 +21828,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -21839,7 +21858,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -21869,7 +21888,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -21899,7 +21918,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -21929,7 +21948,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -21959,7 +21978,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -21989,7 +22008,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>41</v>
       </c>
@@ -22019,7 +22038,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -22049,7 +22068,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>218</v>
       </c>
@@ -22079,7 +22098,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -22109,7 +22128,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>197</v>
       </c>
@@ -22139,7 +22158,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -22169,7 +22188,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -22199,7 +22218,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -22229,7 +22248,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -22259,7 +22278,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>57</v>
       </c>
@@ -22289,7 +22308,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>201</v>
       </c>
@@ -22319,7 +22338,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>59</v>
       </c>
@@ -22349,7 +22368,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -22379,7 +22398,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>183</v>
       </c>
@@ -22409,7 +22428,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>187</v>
       </c>
@@ -22439,7 +22458,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>63</v>
       </c>
@@ -22469,7 +22488,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>65</v>
       </c>
@@ -22499,7 +22518,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>67</v>
       </c>
@@ -22529,7 +22548,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>69</v>
       </c>
@@ -22559,7 +22578,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>219</v>
       </c>
@@ -22589,7 +22608,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>73</v>
       </c>
@@ -22619,7 +22638,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>75</v>
       </c>
@@ -22649,7 +22668,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>77</v>
       </c>
@@ -22679,7 +22698,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>79</v>
       </c>
@@ -22709,7 +22728,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>177</v>
       </c>
@@ -22739,7 +22758,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>81</v>
       </c>
@@ -22769,7 +22788,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>220</v>
       </c>
@@ -22799,7 +22818,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>85</v>
       </c>
@@ -22829,7 +22848,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>87</v>
       </c>
@@ -22859,7 +22878,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>89</v>
       </c>
@@ -22889,7 +22908,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>92</v>
       </c>
@@ -22919,7 +22938,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>94</v>
       </c>
@@ -22949,7 +22968,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>96</v>
       </c>
@@ -22979,7 +22998,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>185</v>
       </c>
@@ -23009,7 +23028,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>99</v>
       </c>
@@ -23039,7 +23058,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>101</v>
       </c>
@@ -23069,7 +23088,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>103</v>
       </c>
@@ -23099,7 +23118,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>105</v>
       </c>
@@ -23129,7 +23148,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>107</v>
       </c>
@@ -23159,7 +23178,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>109</v>
       </c>
@@ -23189,7 +23208,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>191</v>
       </c>
@@ -23219,7 +23238,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>221</v>
       </c>
@@ -23249,7 +23268,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>113</v>
       </c>
@@ -23279,7 +23298,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>222</v>
       </c>
@@ -23309,7 +23328,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>189</v>
       </c>
@@ -23339,7 +23358,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>181</v>
       </c>
@@ -23369,7 +23388,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>117</v>
       </c>
@@ -23399,7 +23418,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>119</v>
       </c>
@@ -23429,7 +23448,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>193</v>
       </c>
@@ -23459,7 +23478,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>121</v>
       </c>
@@ -23489,7 +23508,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>123</v>
       </c>
@@ -23519,7 +23538,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>125</v>
       </c>
@@ -23549,7 +23568,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>127</v>
       </c>
@@ -23582,7 +23601,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>129</v>
       </c>
@@ -23612,7 +23631,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>179</v>
       </c>
@@ -23642,7 +23661,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>131</v>
       </c>
@@ -23675,7 +23694,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>133</v>
       </c>
@@ -23708,7 +23727,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>135</v>
       </c>
@@ -23741,7 +23760,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>137</v>
       </c>
@@ -23774,7 +23793,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>195</v>
       </c>
@@ -23807,7 +23826,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>139</v>
       </c>
@@ -23840,7 +23859,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>141</v>
       </c>
@@ -23873,7 +23892,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>143</v>
       </c>
@@ -23906,7 +23925,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>145</v>
       </c>
@@ -23939,7 +23958,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>147</v>
       </c>
@@ -23972,7 +23991,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>149</v>
       </c>
@@ -24005,7 +24024,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>199</v>
       </c>
@@ -24038,7 +24057,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>151</v>
       </c>
@@ -24071,7 +24090,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>153</v>
       </c>
@@ -24104,7 +24123,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>155</v>
       </c>
@@ -24137,7 +24156,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>157</v>
       </c>
@@ -24170,7 +24189,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>159</v>
       </c>
@@ -24203,7 +24222,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>161</v>
       </c>
@@ -24236,7 +24255,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>163</v>
       </c>
@@ -24263,7 +24282,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>166</v>
       </c>
@@ -24290,7 +24309,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>168</v>
       </c>
@@ -24317,7 +24336,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>170</v>
       </c>
@@ -24350,12 +24369,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="N95" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>205</v>
       </c>
@@ -24381,7 +24400,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>203</v>
       </c>
@@ -24404,7 +24423,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>209</v>
       </c>
@@ -24427,7 +24446,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>211</v>
       </c>
@@ -24450,7 +24469,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>206</v>
       </c>
@@ -24473,7 +24492,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>208</v>
       </c>
@@ -24496,147 +24515,147 @@
         <v>33</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
       <c r="N102" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
       <c r="N103" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
       <c r="N104" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
       <c r="N105" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
       <c r="N106" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
       <c r="N107" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
       <c r="N108" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
       <c r="N109" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
       <c r="N110" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
       <c r="N111" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
       <c r="N112" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="113" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N113" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="114" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N114" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N115" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="116" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N116" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="117" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N117" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="118" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N118" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="119" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N119" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="120" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N120" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="121" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N121" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="122" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N122" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="123" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N123" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="124" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N124" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="125" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N125" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="126" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N126" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="127" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N127" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="128" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N128" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
       <c r="N129" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>2</v>
       </c>
@@ -24644,17 +24663,17 @@
         <v>105</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
       <c r="N131" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
       <c r="N132" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>117</v>
       </c>
@@ -24662,7 +24681,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>127</v>
       </c>
@@ -24670,7 +24689,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>141</v>
       </c>
@@ -24678,7 +24697,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>125</v>
       </c>
@@ -24686,7 +24705,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>43</v>
       </c>
@@ -24694,7 +24713,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>81</v>
       </c>
@@ -24702,7 +24721,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>87</v>
       </c>
@@ -24710,7 +24729,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>73</v>
       </c>
@@ -24718,7 +24737,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>47</v>
       </c>
@@ -24726,7 +24745,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>133</v>
       </c>
@@ -24734,7 +24753,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>147</v>
       </c>
@@ -24742,7 +24761,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>151</v>
       </c>
@@ -24750,7 +24769,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>65</v>
       </c>
@@ -24758,7 +24777,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>53</v>
       </c>
@@ -24766,7 +24785,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>121</v>
       </c>
@@ -24774,7 +24793,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>41</v>
       </c>
@@ -24782,7 +24801,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>51</v>
       </c>
@@ -24790,297 +24809,297 @@
         <v>230</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>230</v>
       </c>
